--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.83483</v>
+        <v>16.78684</v>
       </c>
       <c r="D2" t="n">
-        <v>16.38903</v>
+        <v>16.63381</v>
       </c>
       <c r="E2" t="n">
-        <v>16.87848</v>
+        <v>16.64352</v>
       </c>
       <c r="F2" t="n">
-        <v>42.53636</v>
+        <v>42.32795</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05077</v>
+        <v>0.04948</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81743</v>
+        <v>1.79449</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.96169</v>
+        <v>16.60652</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31319</v>
+        <v>16.08316</v>
       </c>
       <c r="E3" t="n">
-        <v>16.39464</v>
+        <v>16.57249</v>
       </c>
       <c r="F3" t="n">
-        <v>42.87399</v>
+        <v>42.08856</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05072</v>
+        <v>0.05067</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80596</v>
+        <v>1.82522</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.72785</v>
+        <v>16.78608</v>
       </c>
       <c r="D4" t="n">
-        <v>16.49771</v>
+        <v>16.6571</v>
       </c>
       <c r="E4" t="n">
-        <v>16.40753</v>
+        <v>16.6927</v>
       </c>
       <c r="F4" t="n">
-        <v>42.66432</v>
+        <v>42.9089</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05005</v>
+        <v>0.04955</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80485</v>
+        <v>1.79055</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.64754</v>
+        <v>16.59176</v>
       </c>
       <c r="D6" t="n">
-        <v>16.1128</v>
+        <v>15.86679</v>
       </c>
       <c r="E6" t="n">
-        <v>16.69097</v>
+        <v>16.35657</v>
       </c>
       <c r="F6" t="n">
-        <v>21.86949</v>
+        <v>21.71462</v>
       </c>
       <c r="G6" t="n">
-        <v>33.84549</v>
+        <v>34.16778</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.63834</v>
+        <v>17.01675</v>
       </c>
       <c r="D7" t="n">
-        <v>16.03704</v>
+        <v>16.05394</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46035</v>
+        <v>16.12065</v>
       </c>
       <c r="F7" t="n">
-        <v>21.49359</v>
+        <v>21.60876</v>
       </c>
       <c r="G7" t="n">
-        <v>34.02914</v>
+        <v>33.84794</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.58196</v>
+        <v>16.61332</v>
       </c>
       <c r="D8" t="n">
-        <v>15.98307</v>
+        <v>15.83033</v>
       </c>
       <c r="E8" t="n">
-        <v>16.47872</v>
+        <v>16.14596</v>
       </c>
       <c r="F8" t="n">
-        <v>21.61526</v>
+        <v>21.65247</v>
       </c>
       <c r="G8" t="n">
-        <v>34.43547</v>
+        <v>33.57471</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60009</v>
+        <v>0.60419</v>
       </c>
       <c r="D10" t="n">
-        <v>1.09176</v>
+        <v>1.11167</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60381</v>
+        <v>0.59651</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12526</v>
+        <v>1.11462</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59715</v>
+        <v>0.61425</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10502</v>
+        <v>1.08916</v>
       </c>
     </row>
   </sheetData>
